--- a/tests/data_golden/markers.template.xlsx
+++ b/tests/data_golden/markers.template.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
   <si>
     <t>#{r部署}${縦部署#r部署.名前}</t>
   </si>
